--- a/stories/arbres/ATOM-EMO.LEX.007-05.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.007-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Fabien attend dans le salon. Maman prépare le goûter. Les pieds de Fabien tapent. Ses mains froissent le coussin. Fabien dit : je suis nerveux. Maman l'écoute. Maman dit : on peut demander une pause. Fabien dit : je veux une pause. Il s'assoit près de maman. Il souffle une fois. Les pieds se calment. Maman dit : nerveux, ce n'est pas vilain. Une pause, c'est bien. Fabien pose les mains.</t>
+          <t>Fabien attend dans le salon. Maman prépare le goûter. Les pieds de Fabien tapent. Ses mains froissent le coussin. Je suis nerveux. Maman l'écoute. On peut demander une pause. Je veux une pause. Il s'assoit près de maman. Il souffle une fois. Les pieds se calment. Nerveux, ce n'est pas vilain. Une pause, c'est bien. Fabien pose les mains.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Fabien attend dans le salon. Maman prépare le goûter. Les pieds de Fabien tapent. Ses mains froissent le coussin.
+enfant-m|Je suis nerveux. Maman l'écoute.
+maman|On peut demander une pause.
+enfant-m|Je veux une pause.
+narrateur|Il s'assoit près de maman. Il souffle une fois. Les pieds se calment.
+maman|Nerveux, ce n'est pas vilain.
+narrateur|Une pause, c'est bien. Fabien pose les mains.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Fabien n'arrive pas à tenir. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1665,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Fabien a nommé : nerveux. Il a demandé une pause. Il s'est assis.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1832,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Fabien pose les mains. Maman reste près de lui.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1999,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2039,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.007-05.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.007-05.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,7 @@
 narrateur|Une pause, c'est bien. Fabien pose les mains.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1505,7 @@
           <t>narrateur|Fabien n'arrive pas à tenir. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1670,6 +1677,7 @@
           <t>narrateur|Fabien a nommé : nerveux. Il a demandé une pause. Il s'est assis.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1837,6 +1845,7 @@
           <t>narrateur|Fabien pose les mains. Maman reste près de lui.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2004,6 +2013,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2022,7 +2032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2046,6 +2056,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2247,6 +2271,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-EMO.LEX.007-05.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.007-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Fabien demande une pause</t>
+          <t>Nino demande une pause</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Nino attend le cacao. Il est nerveux. Il demande une pause. Il s'assoit près de maman.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Fabien attend dans le salon. Maman prépare le goûter. Les pieds de Fabien tapent. Ses mains froissent le coussin. Je suis nerveux. Maman l'écoute. On peut demander une pause. Je veux une pause. Il s'assoit près de maman. Il souffle une fois. Les pieds se calment. Nerveux, ce n'est pas vilain. Une pause, c'est bien. Fabien pose les mains.</t>
+          <t>La gouttière fait tic, tic, tic. La pluie glisse sur la vitre. Dans la maison, ça sent le cacao. Une boîte rouge attend sur la table. Dedans, un biscuit rond. Le couvercle de la boîte est froid. Le tapis du salon est bleu. Un coussin jaune est sur le canapé. Le coussin est un peu chaud. Une goutte glisse sur la vitre. Nino, le cacao est presque prêt. Ça sent bon, maman. Oui. Encore un tout petit moment. En ce moment, Nino attend. Il est dans le salon. Ses pieds tapent le tapis. Tap, tap, tap. Ses mains froissent le coussin jaune. Le tissu est doux sous les doigts. Maman, j'attends. Je t'écoute, Nino. Je suis nerveux. Tu es nerveux. Ce n'est pas vilain. On peut demander une pause. Je veux une pause. Viens. Assieds-toi près de moi. Nino s'assoit près de maman. Le canapé est moelleux. Souffle une fois, tout doux. Nino souffle une fois. Ses pieds se calment. Ses mains se posent. Nerveux, ce n'est pas vilain. Une pause, c'est bien. Je me pose. Bravo, Nino. C'est du bon travail. Tes pieds sont plus calmes ? Oui, maman. On regarde la goutte, ensemble ? Elle glisse tout doux. Comme toi, maintenant. Le cacao arrive tout de suite. La gouttière fait encore tic, tic. Le coussin jaune reste près de lui. Tu as demandé une pause. Oui. J'étais nerveux. Et maintenant, on goûte.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,16 +1324,65 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Fabien attend dans le salon. Maman prépare le goûter. Les pieds de Fabien tapent. Ses mains froissent le coussin.
-enfant-m|Je suis nerveux. Maman l'écoute.
+          <t>narrateur|La gouttière fait tic, tic, tic.
+narrateur|La pluie glisse sur la vitre.
+narrateur|Dans la maison, ça sent le cacao.
+narrateur|Une boîte rouge attend sur la table.
+narrateur|Dedans, un biscuit rond.
+narrateur|Le couvercle de la boîte est froid.
+narrateur|Le tapis du salon est bleu.
+narrateur|Un coussin jaune est sur le canapé.
+narrateur|Le coussin est un peu chaud.
+narrateur|Une goutte glisse sur la vitre.
+maman|Nino, le cacao est presque prêt.
+enfant-m|Ça sent bon, maman.
+maman|Oui.
+maman|Encore un tout petit moment.
+narrateur|En ce moment, Nino attend.
+narrateur|Il est dans le salon.
+narrateur|Ses pieds tapent le tapis.
+narrateur|Tap, tap, tap.
+narrateur|Ses mains froissent le coussin jaune.
+narrateur|Le tissu est doux sous les doigts.
+enfant-m|Maman, j'attends.
+maman|Je t'écoute, Nino.
+enfant-m|Je suis nerveux.
+maman|Tu es nerveux.
+maman|Ce n'est pas vilain.
 maman|On peut demander une pause.
 enfant-m|Je veux une pause.
-narrateur|Il s'assoit près de maman. Il souffle une fois. Les pieds se calment.
+maman|Viens.
+maman|Assieds-toi près de moi.
+narrateur|Nino s'assoit près de maman.
+narrateur|Le canapé est moelleux.
+maman|Souffle une fois, tout doux.
+narrateur|Nino souffle une fois.
+narrateur|Ses pieds se calment.
+narrateur|Ses mains se posent.
 maman|Nerveux, ce n'est pas vilain.
-narrateur|Une pause, c'est bien. Fabien pose les mains.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+maman|Une pause, c'est bien.
+enfant-m|Je me pose.
+maman|Bravo, Nino.
+maman|C'est du bon travail.
+maman|Tes pieds sont plus calmes ?
+enfant-m|Oui, maman.
+maman|On regarde la goutte, ensemble ?
+enfant-m|Elle glisse tout doux.
+maman|Comme toi, maintenant.
+maman|Le cacao arrive tout de suite.
+narrateur|La gouttière fait encore tic, tic.
+narrateur|Le coussin jaune reste près de lui.
+maman|Tu as demandé une pause.
+enfant-m|Oui.
+enfant-m|J'étais nerveux.
+maman|Et maintenant, on goûte.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>pluie</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1346,7 +1407,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Fabien n'arrive pas à tenir. Que fait-il ?</t>
+          <t>Nino n'arrive pas à tenir. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1502,7 +1563,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Fabien n'arrive pas à tenir. Que fait-il ?</t>
+          <t>narrateur|Nino n'arrive pas à tenir.
+narrateur|Que fait-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1530,7 +1592,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Fabien a nommé : nerveux. Il a demandé une pause. Il s'est assis.</t>
+          <t>Nino a nommé : nerveux. Il a demandé une pause. Il s'est assis près de maman. Je suis nerveux. Je veux une pause. Oui. Tu t'es assis. Bravo. C'est du bon travail. Le cacao fume un peu. La tasse est chaude, tout doux. Tu poses les mains sur tes genoux ? Oui. Elles sont calmes. Nerveux, ce n'est pas vilain. Une pause aide le corps. Le biscuit attend dans l'assiette. On souffle encore une fois ? Oui. Tout petit.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1674,7 +1736,26 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Fabien a nommé : nerveux. Il a demandé une pause. Il s'est assis.</t>
+          <t>narrateur|Nino a nommé : nerveux.
+narrateur|Il a demandé une pause.
+narrateur|Il s'est assis près de maman.
+enfant-m|Je suis nerveux.
+enfant-m|Je veux une pause.
+maman|Oui.
+maman|Tu t'es assis.
+maman|Bravo.
+maman|C'est du bon travail.
+narrateur|Le cacao fume un peu.
+narrateur|La tasse est chaude, tout doux.
+maman|Tu poses les mains sur tes genoux ?
+enfant-m|Oui.
+enfant-m|Elles sont calmes.
+maman|Nerveux, ce n'est pas vilain.
+maman|Une pause aide le corps.
+narrateur|Le biscuit attend dans l'assiette.
+maman|On souffle encore une fois ?
+enfant-m|Oui.
+enfant-m|Tout petit.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1702,7 +1783,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Fabien pose les mains. Maman reste près de lui.</t>
+          <t>Nino pose les mains. Le biscuit est dans l'assiette. On reste assis un peu ? Oui. Près de toi. Je t'écoute. Le cacao est chaud. On souffle dessus, ensemble. Ils soufflent une petite fois. La pluie tapote encore la vitre. Tu as demandé ta pause. C'est du bon travail, Nino. Je suis moins nerveux. Le coussin jaune reste sur le canapé. La boîte rouge reste sur la table.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1842,7 +1923,21 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Fabien pose les mains. Maman reste près de lui.</t>
+          <t>narrateur|Nino pose les mains.
+narrateur|Le biscuit est dans l'assiette.
+maman|On reste assis un peu ?
+enfant-m|Oui.
+enfant-m|Près de toi.
+maman|Je t'écoute.
+enfant-m|Le cacao est chaud.
+maman|On souffle dessus, ensemble.
+narrateur|Ils soufflent une petite fois.
+narrateur|La pluie tapote encore la vitre.
+maman|Tu as demandé ta pause.
+maman|C'est du bon travail, Nino.
+enfant-m|Je suis moins nerveux.
+narrateur|Le coussin jaune reste sur le canapé.
+narrateur|La boîte rouge reste sur la table.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1870,7 +1965,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'étais nerveux. J'ai demandé une pause. Bravo, Nino. Tu as fait du bon travail. La gouttière fait encore tic, tic. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2010,7 +2105,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'étais nerveux.
+enfant-m|J'ai demandé une pause.
+maman|Bravo, Nino.
+maman|Tu as fait du bon travail.
+narrateur|La gouttière fait encore tic, tic.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2032,7 +2132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2070,6 +2170,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.007-05.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.007-05.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La gouttière fait tic, tic, tic. La pluie glisse sur la vitre. Dans la maison, ça sent le cacao. Une boîte rouge attend sur la table. Dedans, un biscuit rond. Le couvercle de la boîte est froid. Le tapis du salon est bleu. Un coussin jaune est sur le canapé. Le coussin est un peu chaud. Une goutte glisse sur la vitre. Nino, le cacao est presque prêt. Ça sent bon, maman. Oui. Encore un tout petit moment. En ce moment, Nino attend. Il est dans le salon. Ses pieds tapent le tapis. Tap, tap, tap. Ses mains froissent le coussin jaune. Le tissu est doux sous les doigts. Maman, j'attends. Je t'écoute, Nino. Je suis nerveux. Tu es nerveux. Ce n'est pas vilain. On peut demander une pause. Je veux une pause. Viens. Assieds-toi près de moi. Nino s'assoit près de maman. Le canapé est moelleux. Souffle une fois, tout doux. Nino souffle une fois. Ses pieds se calment. Ses mains se posent. Nerveux, ce n'est pas vilain. Une pause, c'est bien. Je me pose. Bravo, Nino. C'est du bon travail. Tes pieds sont plus calmes ? Oui, maman. On regarde la goutte, ensemble ? Elle glisse tout doux. Comme toi, maintenant. Le cacao arrive tout de suite. La gouttière fait encore tic, tic. Le coussin jaune reste près de lui. Tu as demandé une pause. Oui. J'étais nerveux. Et maintenant, on goûte.</t>
+          <t>La gouttière fait tic, tic, tic. La pluie glisse sur la vitre. Dans la maison, ça sent le cacao. Une boîte rouge attend sur la table. Dedans, un biscuit rond. Le couvercle de la boîte est froid. Le tapis du salon est bleu. Un coussin jaune est sur le canapé. Le coussin est un peu chaud. Une goutte glisse sur la vitre. Nino, le cacao est presque prêt. Ça sent bon, maman. Oui. Encore un tout petit moment. En ce moment, Nino attend. Il est dans le salon. Ses pieds tapent le tapis. Tap, tap, tap. Ses mains froissent le coussin jaune. Le tissu est doux sous les doigts. Maman, j'attends. Je t'écoute, Nino. Je suis nerveux. Tu es nerveux. Ce n'est pas vilain. On peut demander une pause. Je veux une pause. Viens. Assieds-toi près de moi. Nino s'assoit près de maman. Le canapé est moelleux. Souffle une fois, tout doux. Nino souffle une fois. Ses pieds se calment. Ses mains se posent. Nerveux, ce n'est pas vilain. Une pause, c'est bien. Je me pose. Bravo, Nino. Tes pieds sont plus calmes ? Oui, maman. On regarde la goutte, ensemble ? Elle glisse tout doux. Comme toi, maintenant. Le cacao arrive tout de suite. La gouttière fait encore tic, tic. Le coussin jaune reste près de lui. Tu as demandé une pause. Oui. J'étais nerveux. Et maintenant, on goûte.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Fabien attend dans le salon. Maman prépare le goûter. Les pieds de Fabien tapent. Ses mains froissent le coussin. Fabien dit : je suis &lt;emphasis level="moderate"&gt;nerveux&lt;/emphasis&gt;. Maman l'écoute. Maman dit : on peut demander une pause. Fabien dit : je veux une pause. Il s'assoit près de maman. Il souffle une fois. Les pieds se calment. Maman dit : nerveux, ce n'est pas vilain. Une pause, c'est bien. Fabien pose les mains.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La gouttière fait tic, tic, tic. La pluie glisse sur la vitre. Dans la maison, ça sent le cacao. Une boîte rouge attend sur la table. Dedans, un biscuit rond. Le couvercle de la boîte est froid. Le tapis du salon est bleu. Un coussin jaune est sur le canapé. Le coussin est un peu chaud. Une goutte glisse sur la vitre. Nino, le cacao est presque prêt. Ça sent bon, maman. Oui. Encore un tout petit moment. En ce moment, Nino attend. Il est dans le salon. Ses pieds tapent le tapis. Tap, tap, tap. Ses mains froissent le coussin jaune. Le tissu est doux sous les doigts. Maman, j'attends. Je t'écoute, Nino. Je suis nerveux. Tu es nerveux. Ce n'est pas vilain. On peut demander une pause. Je veux une pause. Viens. Assieds-toi près de moi. Nino s'assoit près de maman. Le canapé est moelleux. Souffle une fois, tout doux. Nino souffle une fois. Ses pieds se calment. Ses mains se posent. Nerveux, ce n'est pas vilain. Une pause, c'est bien. Je me pose. Bravo, Nino. Tes pieds sont plus calmes ? Oui, maman. On regarde la goutte, ensemble ? Elle glisse tout doux. Comme toi, maintenant. Le cacao arrive tout de suite. La gouttière fait encore tic, tic. Le coussin jaune reste près de lui. Tu as demandé une pause. Oui. J'étais nerveux. Et maintenant, on goûte.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1363,7 +1363,6 @@
 maman|Une pause, c'est bien.
 enfant-m|Je me pose.
 maman|Bravo, Nino.
-maman|C'est du bon travail.
 maman|Tes pieds sont plus calmes ?
 enfant-m|Oui, maman.
 maman|On regarde la goutte, ensemble ?
@@ -1412,7 +1411,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Fabien n'arrive pas à tenir. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino n'arrive pas à tenir. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1567,7 +1566,6 @@
 narrateur|Que fait-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1592,12 +1590,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nino a nommé : nerveux. Il a demandé une pause. Il s'est assis près de maman. Je suis nerveux. Je veux une pause. Oui. Tu t'es assis. Bravo. C'est du bon travail. Le cacao fume un peu. La tasse est chaude, tout doux. Tu poses les mains sur tes genoux ? Oui. Elles sont calmes. Nerveux, ce n'est pas vilain. Une pause aide le corps. Le biscuit attend dans l'assiette. On souffle encore une fois ? Oui. Tout petit.</t>
+          <t>Nino a nommé : nerveux. Il a demandé une pause. Il s'est assis près de maman. Je suis nerveux. Je veux une pause. Oui. Tu t'es assis. Bravo. Le cacao fume un peu. La tasse est chaude, tout doux. Tu poses les mains sur tes genoux ? Oui. Elles sont calmes. Nerveux, ce n'est pas vilain. Une pause aide le corps. Le biscuit attend dans l'assiette. On souffle encore une fois ? Oui. Tout petit.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Fabien a nommé : &lt;emphasis level="moderate"&gt;nerveux&lt;/emphasis&gt;. Il a demandé une pause. Il s'est assis.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino a nommé : nerveux. Il a demandé une pause. Il s'est assis près de maman. Je suis nerveux. Je veux une pause. Oui. Tu t'es assis. Bravo. Le cacao fume un peu. La tasse est chaude, tout doux. Tu poses les mains sur tes genoux ? Oui. Elles sont calmes. Nerveux, ce n'est pas vilain. Une pause aide le corps. Le biscuit attend dans l'assiette. On souffle encore une fois ? Oui. Tout petit.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1744,7 +1742,6 @@
 maman|Oui.
 maman|Tu t'es assis.
 maman|Bravo.
-maman|C'est du bon travail.
 narrateur|Le cacao fume un peu.
 narrateur|La tasse est chaude, tout doux.
 maman|Tu poses les mains sur tes genoux ?
@@ -1758,7 +1755,6 @@
 enfant-m|Tout petit.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1783,12 +1779,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Nino pose les mains. Le biscuit est dans l'assiette. On reste assis un peu ? Oui. Près de toi. Je t'écoute. Le cacao est chaud. On souffle dessus, ensemble. Ils soufflent une petite fois. La pluie tapote encore la vitre. Tu as demandé ta pause. C'est du bon travail, Nino. Je suis moins nerveux. Le coussin jaune reste sur le canapé. La boîte rouge reste sur la table.</t>
+          <t>Nino pose les mains. Le biscuit est dans l'assiette. On reste assis un peu ? Oui. Près de toi. Je t'écoute. Le cacao est chaud. On souffle dessus, ensemble. Ils soufflent une petite fois. La pluie tapote encore la vitre. Tu as demandé ta pause. Je suis moins nerveux. Le coussin jaune reste sur le canapé. La boîte rouge reste sur la table.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Fabien pose les &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt;s. Maman reste près de lui.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino pose les mains. Le biscuit est dans l'assiette. On reste assis un peu ? Oui. Près de toi. Je t'écoute. Le cacao est chaud. On souffle dessus, ensemble. Ils soufflent une petite fois. La pluie tapote encore la vitre. Tu as demandé ta pause. Je suis moins nerveux. Le coussin jaune reste sur le canapé. La boîte rouge reste sur la table.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1934,13 +1930,11 @@
 narrateur|Ils soufflent une petite fois.
 narrateur|La pluie tapote encore la vitre.
 maman|Tu as demandé ta pause.
-maman|C'est du bon travail, Nino.
 enfant-m|Je suis moins nerveux.
 narrateur|Le coussin jaune reste sur le canapé.
 narrateur|La boîte rouge reste sur la table.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1965,12 +1959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'étais nerveux. J'ai demandé une pause. Bravo, Nino. Tu as fait du bon travail. La gouttière fait encore tic, tic. L'histoire est finie.</t>
+          <t>J'étais nerveux. J'ai demandé une pause. Bravo, Nino. La gouttière fait encore tic, tic.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'étais nerveux. J'ai demandé une pause. Bravo, Nino. La gouttière fait encore tic, tic.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2108,12 +2102,9 @@
           <t>enfant-m|J'étais nerveux.
 enfant-m|J'ai demandé une pause.
 maman|Bravo, Nino.
-maman|Tu as fait du bon travail.
-narrateur|La gouttière fait encore tic, tic.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|La gouttière fait encore tic, tic.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2132,7 +2123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2177,6 +2168,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.007-05.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.007-05.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Fabien, maman</t>
+          <t>Nino, maman</t>
         </is>
       </c>
     </row>
